--- a/MultiCellBMSConfig/NMC/Experiment_6_NMC_Configuration.xlsx
+++ b/MultiCellBMSConfig/NMC/Experiment_6_NMC_Configuration.xlsx
@@ -461,6 +461,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -572,7 +573,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - Variable-Length CAN Mode: Set parser_type = 'waveshare_can' or 'variable_length' (Header 0xAA, DLC, CAN ID, payload, footer 0x55).</t>
+          <t xml:space="preserve">   - Variable-Length CAN Mode: Set parser_type = 'waveshare_can_variable_length' (Variable-Length CAN) (Header 0xAA, DLC, CAN ID, payload, footer 0x55).</t>
         </is>
       </c>
     </row>
@@ -590,6 +591,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
@@ -938,7 +940,6 @@
           <t>header_to_payload</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>none</t>
@@ -962,7 +963,7 @@
   </sheetData>
   <dataValidations count="13">
     <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"framed,waveshare_can,waveshare_can_20_bytes"</formula1>
+      <formula1>"framed,waveshare_can_variable_length,waveshare_can_20_bytes"</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"1,2,4"</formula1>
@@ -1553,7 +1554,6 @@
       <c r="D2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>little</t>
@@ -1614,7 +1614,6 @@
       <c r="D3" t="n">
         <v>1</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>little</t>
@@ -1927,7 +1926,6 @@
       <c r="D8" t="n">
         <v>1</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>little</t>
@@ -2177,7 +2175,6 @@
       <c r="D12" t="n">
         <v>1</v>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>little</t>
@@ -2301,7 +2298,6 @@
       <c r="D14" t="n">
         <v>1</v>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>little</t>
@@ -2362,7 +2358,6 @@
       <c r="D15" t="n">
         <v>1</v>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>little</t>
@@ -2423,7 +2418,6 @@
       <c r="D16" t="n">
         <v>1</v>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>little</t>
@@ -2484,7 +2478,6 @@
       <c r="D17" t="n">
         <v>1</v>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>little</t>
@@ -2545,7 +2538,6 @@
       <c r="D18" t="n">
         <v>1</v>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>little</t>
@@ -2606,7 +2598,6 @@
       <c r="D19" t="n">
         <v>1</v>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>little</t>
@@ -2667,7 +2658,6 @@
       <c r="D20" t="n">
         <v>1</v>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>little</t>
@@ -2728,7 +2718,6 @@
       <c r="D21" t="n">
         <v>1</v>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>little</t>
@@ -2789,7 +2778,6 @@
       <c r="D22" t="n">
         <v>1</v>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>little</t>
@@ -2850,7 +2838,6 @@
       <c r="D23" t="n">
         <v>1</v>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>little</t>
@@ -2911,7 +2898,6 @@
       <c r="D24" t="n">
         <v>1</v>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>little</t>
@@ -3937,7 +3923,6 @@
           <t>V</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="b">
         <v>1</v>
       </c>
@@ -3958,7 +3943,6 @@
           <t>V</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="b">
         <v>1</v>
       </c>
@@ -3979,7 +3963,6 @@
           <t>°C</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="b">
         <v>1</v>
       </c>
